--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37534,13 +37534,13 @@
         <v>46276.5625</v>
       </c>
       <c r="B1430" t="n">
-        <v>15220682</v>
+        <v>15329000</v>
       </c>
       <c r="C1430" t="n">
         <v>37.939998626709</v>
       </c>
       <c r="D1430" t="n">
-        <v>36.3320999145508</v>
+        <v>36.3320007324219</v>
       </c>
       <c r="E1430" t="n">
         <v>37.2299995422363</v>
@@ -37552,6 +37552,32 @@
         <v>36.75</v>
       </c>
       <c r="H1430" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" s="1" t="n">
+        <v>46279.5625</v>
+      </c>
+      <c r="B1431" t="n">
+        <v>18159357</v>
+      </c>
+      <c r="C1431" t="n">
+        <v>38.560001373291</v>
+      </c>
+      <c r="D1431" t="n">
+        <v>35</v>
+      </c>
+      <c r="E1431" t="n">
+        <v>35.1599998474121</v>
+      </c>
+      <c r="F1431" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="G1431" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="H1431" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37534,7 +37534,7 @@
         <v>46276.5625</v>
       </c>
       <c r="B1430" t="n">
-        <v>15329000</v>
+        <v>15395500</v>
       </c>
       <c r="C1430" t="n">
         <v>37.939998626709</v>
@@ -37560,7 +37560,7 @@
         <v>46279.5625</v>
       </c>
       <c r="B1431" t="n">
-        <v>18159357</v>
+        <v>18228800</v>
       </c>
       <c r="C1431" t="n">
         <v>38.560001373291</v>
@@ -37578,6 +37578,32 @@
         <v>37.5</v>
       </c>
       <c r="H1431" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" s="1" t="n">
+        <v>46280.5625</v>
+      </c>
+      <c r="B1432" t="n">
+        <v>12848280</v>
+      </c>
+      <c r="C1432" t="n">
+        <v>38.1599998474121</v>
+      </c>
+      <c r="D1432" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="E1432" t="n">
+        <v>36.2750015258789</v>
+      </c>
+      <c r="F1432" t="n">
+        <v>37.0499992370605</v>
+      </c>
+      <c r="G1432" t="n">
+        <v>37.0499992370605</v>
+      </c>
+      <c r="H1432" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37586,10 +37586,10 @@
         <v>46280.5625</v>
       </c>
       <c r="B1432" t="n">
-        <v>12848280</v>
+        <v>12906800</v>
       </c>
       <c r="C1432" t="n">
-        <v>38.1599998474121</v>
+        <v>38.1699981689453</v>
       </c>
       <c r="D1432" t="n">
         <v>36.2599983215332</v>
@@ -37604,6 +37604,32 @@
         <v>37.0499992370605</v>
       </c>
       <c r="H1432" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" s="1" t="n">
+        <v>46281.5625</v>
+      </c>
+      <c r="B1433" t="n">
+        <v>15690868</v>
+      </c>
+      <c r="C1433" t="n">
+        <v>37.6500015258789</v>
+      </c>
+      <c r="D1433" t="n">
+        <v>36.0601005554199</v>
+      </c>
+      <c r="E1433" t="n">
+        <v>36.9799995422363</v>
+      </c>
+      <c r="F1433" t="n">
+        <v>36.8400001525879</v>
+      </c>
+      <c r="G1433" t="n">
+        <v>36.8400001525879</v>
+      </c>
+      <c r="H1433" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37612,13 +37612,13 @@
         <v>46281.5625</v>
       </c>
       <c r="B1433" t="n">
-        <v>15690868</v>
+        <v>15823800</v>
       </c>
       <c r="C1433" t="n">
         <v>37.6500015258789</v>
       </c>
       <c r="D1433" t="n">
-        <v>36.0601005554199</v>
+        <v>36.060001373291</v>
       </c>
       <c r="E1433" t="n">
         <v>36.9799995422363</v>
@@ -37630,6 +37630,32 @@
         <v>36.8400001525879</v>
       </c>
       <c r="H1433" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" s="1" t="n">
+        <v>46282.5625</v>
+      </c>
+      <c r="B1434" t="n">
+        <v>22359868</v>
+      </c>
+      <c r="C1434" t="n">
+        <v>40.7798004150391</v>
+      </c>
+      <c r="D1434" t="n">
+        <v>38.1100006103516</v>
+      </c>
+      <c r="E1434" t="n">
+        <v>38.3199996948242</v>
+      </c>
+      <c r="F1434" t="n">
+        <v>40.3400001525879</v>
+      </c>
+      <c r="G1434" t="n">
+        <v>40.3400001525879</v>
+      </c>
+      <c r="H1434" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37638,13 +37638,13 @@
         <v>46282.5625</v>
       </c>
       <c r="B1434" t="n">
-        <v>22359868</v>
+        <v>22494900</v>
       </c>
       <c r="C1434" t="n">
-        <v>40.7798004150391</v>
+        <v>40.7799987792969</v>
       </c>
       <c r="D1434" t="n">
-        <v>38.1100006103516</v>
+        <v>38.0900001525879</v>
       </c>
       <c r="E1434" t="n">
         <v>38.3199996948242</v>
@@ -37656,6 +37656,32 @@
         <v>40.3400001525879</v>
       </c>
       <c r="H1434" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" s="1" t="n">
+        <v>46283.5625</v>
+      </c>
+      <c r="B1435" t="n">
+        <v>22841359</v>
+      </c>
+      <c r="C1435" t="n">
+        <v>40.9444007873535</v>
+      </c>
+      <c r="D1435" t="n">
+        <v>37.7700004577637</v>
+      </c>
+      <c r="E1435" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="F1435" t="n">
+        <v>39.1300010681152</v>
+      </c>
+      <c r="G1435" t="n">
+        <v>39.1300010681152</v>
+      </c>
+      <c r="H1435" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37664,10 +37664,10 @@
         <v>46283.5625</v>
       </c>
       <c r="B1435" t="n">
-        <v>22841359</v>
+        <v>23052200</v>
       </c>
       <c r="C1435" t="n">
-        <v>40.9444007873535</v>
+        <v>40.9440002441406</v>
       </c>
       <c r="D1435" t="n">
         <v>37.7700004577637</v>
@@ -37682,6 +37682,32 @@
         <v>39.1300010681152</v>
       </c>
       <c r="H1435" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" s="1" t="n">
+        <v>46286.5625</v>
+      </c>
+      <c r="B1436" t="n">
+        <v>14112728</v>
+      </c>
+      <c r="C1436" t="n">
+        <v>40.9300003051758</v>
+      </c>
+      <c r="D1436" t="n">
+        <v>39.8400001525879</v>
+      </c>
+      <c r="E1436" t="n">
+        <v>40.4300003051758</v>
+      </c>
+      <c r="F1436" t="n">
+        <v>40.5099983215332</v>
+      </c>
+      <c r="G1436" t="n">
+        <v>40.5099983215332</v>
+      </c>
+      <c r="H1436" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37664,7 +37664,7 @@
         <v>46283.5625</v>
       </c>
       <c r="B1435" t="n">
-        <v>23052200</v>
+        <v>23126600</v>
       </c>
       <c r="C1435" t="n">
         <v>40.9440002441406</v>
@@ -37690,13 +37690,13 @@
         <v>46286.5625</v>
       </c>
       <c r="B1436" t="n">
-        <v>14112728</v>
+        <v>14289400</v>
       </c>
       <c r="C1436" t="n">
         <v>40.9300003051758</v>
       </c>
       <c r="D1436" t="n">
-        <v>39.8400001525879</v>
+        <v>39.8300018310547</v>
       </c>
       <c r="E1436" t="n">
         <v>40.4300003051758</v>
@@ -37708,6 +37708,32 @@
         <v>40.5099983215332</v>
       </c>
       <c r="H1436" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" s="1" t="n">
+        <v>46287.5625</v>
+      </c>
+      <c r="B1437" t="n">
+        <v>15169507</v>
+      </c>
+      <c r="C1437" t="n">
+        <v>40.7999992370605</v>
+      </c>
+      <c r="D1437" t="n">
+        <v>39.8699989318848</v>
+      </c>
+      <c r="E1437" t="n">
+        <v>40.5099983215332</v>
+      </c>
+      <c r="F1437" t="n">
+        <v>40.7400016784668</v>
+      </c>
+      <c r="G1437" t="n">
+        <v>40.7400016784668</v>
+      </c>
+      <c r="H1437" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37716,7 +37716,7 @@
         <v>46287.5625</v>
       </c>
       <c r="B1437" t="n">
-        <v>15169507</v>
+        <v>17857200</v>
       </c>
       <c r="C1437" t="n">
         <v>40.7999992370605</v>
@@ -37734,6 +37734,32 @@
         <v>40.7400016784668</v>
       </c>
       <c r="H1437" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" s="1" t="n">
+        <v>46288.5625</v>
+      </c>
+      <c r="B1438" t="n">
+        <v>72152387</v>
+      </c>
+      <c r="C1438" t="n">
+        <v>46.0229988098145</v>
+      </c>
+      <c r="D1438" t="n">
+        <v>41.6300010681152</v>
+      </c>
+      <c r="E1438" t="n">
+        <v>45.8400001525879</v>
+      </c>
+      <c r="F1438" t="n">
+        <v>42.5400009155273</v>
+      </c>
+      <c r="G1438" t="n">
+        <v>42.5400009155273</v>
+      </c>
+      <c r="H1438" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37742,10 +37742,10 @@
         <v>46288.5625</v>
       </c>
       <c r="B1438" t="n">
-        <v>72152387</v>
+        <v>72555700</v>
       </c>
       <c r="C1438" t="n">
-        <v>46.0229988098145</v>
+        <v>46.0499992370605</v>
       </c>
       <c r="D1438" t="n">
         <v>41.6300010681152</v>
@@ -37760,6 +37760,32 @@
         <v>42.5400009155273</v>
       </c>
       <c r="H1438" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" s="1" t="n">
+        <v>46289.5625</v>
+      </c>
+      <c r="B1439" t="n">
+        <v>42993459</v>
+      </c>
+      <c r="C1439" t="n">
+        <v>45.6599998474121</v>
+      </c>
+      <c r="D1439" t="n">
+        <v>41.2799987792969</v>
+      </c>
+      <c r="E1439" t="n">
+        <v>41.5699996948242</v>
+      </c>
+      <c r="F1439" t="n">
+        <v>44.9799995422363</v>
+      </c>
+      <c r="G1439" t="n">
+        <v>44.9799995422363</v>
+      </c>
+      <c r="H1439" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37768,7 +37768,7 @@
         <v>46289.5625</v>
       </c>
       <c r="B1439" t="n">
-        <v>42993459</v>
+        <v>43226800</v>
       </c>
       <c r="C1439" t="n">
         <v>45.6599998474121</v>
@@ -37786,6 +37786,32 @@
         <v>44.9799995422363</v>
       </c>
       <c r="H1439" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" s="1" t="n">
+        <v>46290.5625</v>
+      </c>
+      <c r="B1440" t="n">
+        <v>27399933</v>
+      </c>
+      <c r="C1440" t="n">
+        <v>46.5499000549316</v>
+      </c>
+      <c r="D1440" t="n">
+        <v>44.1199989318848</v>
+      </c>
+      <c r="E1440" t="n">
+        <v>44.7000007629395</v>
+      </c>
+      <c r="F1440" t="n">
+        <v>45.4799995422363</v>
+      </c>
+      <c r="G1440" t="n">
+        <v>45.4799995422363</v>
+      </c>
+      <c r="H1440" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37794,10 +37794,10 @@
         <v>46290.5625</v>
       </c>
       <c r="B1440" t="n">
-        <v>27399933</v>
+        <v>27472800</v>
       </c>
       <c r="C1440" t="n">
-        <v>46.5499000549316</v>
+        <v>46.5499992370605</v>
       </c>
       <c r="D1440" t="n">
         <v>44.1199989318848</v>
@@ -37812,6 +37812,32 @@
         <v>45.4799995422363</v>
       </c>
       <c r="H1440" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" s="1" t="n">
+        <v>46293.5625</v>
+      </c>
+      <c r="B1441" t="n">
+        <v>34865379</v>
+      </c>
+      <c r="C1441" t="n">
+        <v>47.9099998474121</v>
+      </c>
+      <c r="D1441" t="n">
+        <v>44.5400009155273</v>
+      </c>
+      <c r="E1441" t="n">
+        <v>45.6399993896484</v>
+      </c>
+      <c r="F1441" t="n">
+        <v>44.5800018310547</v>
+      </c>
+      <c r="G1441" t="n">
+        <v>44.5800018310547</v>
+      </c>
+      <c r="H1441" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37794,7 +37794,7 @@
         <v>46290.5625</v>
       </c>
       <c r="B1440" t="n">
-        <v>27472800</v>
+        <v>27579200</v>
       </c>
       <c r="C1440" t="n">
         <v>46.5499992370605</v>
@@ -37820,7 +37820,7 @@
         <v>46293.5625</v>
       </c>
       <c r="B1441" t="n">
-        <v>34865379</v>
+        <v>35027400</v>
       </c>
       <c r="C1441" t="n">
         <v>47.9099998474121</v>
@@ -37838,6 +37838,32 @@
         <v>44.5800018310547</v>
       </c>
       <c r="H1441" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" s="1" t="n">
+        <v>46294.5625</v>
+      </c>
+      <c r="B1442" t="n">
+        <v>18688284</v>
+      </c>
+      <c r="C1442" t="n">
+        <v>45.9043998718262</v>
+      </c>
+      <c r="D1442" t="n">
+        <v>43.7249984741211</v>
+      </c>
+      <c r="E1442" t="n">
+        <v>45.7999992370605</v>
+      </c>
+      <c r="F1442" t="n">
+        <v>43.9099998474121</v>
+      </c>
+      <c r="G1442" t="n">
+        <v>43.9099998474121</v>
+      </c>
+      <c r="H1442" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37846,10 +37846,10 @@
         <v>46294.5625</v>
       </c>
       <c r="B1442" t="n">
-        <v>18688284</v>
+        <v>18797000</v>
       </c>
       <c r="C1442" t="n">
-        <v>45.9043998718262</v>
+        <v>45.9039993286133</v>
       </c>
       <c r="D1442" t="n">
         <v>43.7249984741211</v>
@@ -37864,6 +37864,32 @@
         <v>43.9099998474121</v>
       </c>
       <c r="H1442" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" s="1" t="n">
+        <v>46295.5625</v>
+      </c>
+      <c r="B1443" t="n">
+        <v>25405090</v>
+      </c>
+      <c r="C1443" t="n">
+        <v>47.3300018310547</v>
+      </c>
+      <c r="D1443" t="n">
+        <v>43.814998626709</v>
+      </c>
+      <c r="E1443" t="n">
+        <v>44.2400016784668</v>
+      </c>
+      <c r="F1443" t="n">
+        <v>43.8600006103516</v>
+      </c>
+      <c r="G1443" t="n">
+        <v>43.8600006103516</v>
+      </c>
+      <c r="H1443" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37872,7 +37872,7 @@
         <v>46295.5625</v>
       </c>
       <c r="B1443" t="n">
-        <v>25405090</v>
+        <v>25553100</v>
       </c>
       <c r="C1443" t="n">
         <v>47.3300018310547</v>
@@ -37890,6 +37890,32 @@
         <v>43.8600006103516</v>
       </c>
       <c r="H1443" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" s="1" t="n">
+        <v>46296.5625</v>
+      </c>
+      <c r="B1444" t="n">
+        <v>17104273</v>
+      </c>
+      <c r="C1444" t="n">
+        <v>45.089900970459</v>
+      </c>
+      <c r="D1444" t="n">
+        <v>43.5499992370605</v>
+      </c>
+      <c r="E1444" t="n">
+        <v>43.9500007629395</v>
+      </c>
+      <c r="F1444" t="n">
+        <v>43.9900016784668</v>
+      </c>
+      <c r="G1444" t="n">
+        <v>43.9900016784668</v>
+      </c>
+      <c r="H1444" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37898,10 +37898,10 @@
         <v>46296.5625</v>
       </c>
       <c r="B1444" t="n">
-        <v>17104273</v>
+        <v>17214100</v>
       </c>
       <c r="C1444" t="n">
-        <v>45.089900970459</v>
+        <v>45.0900001525879</v>
       </c>
       <c r="D1444" t="n">
         <v>43.5499992370605</v>
@@ -37916,6 +37916,32 @@
         <v>43.9900016784668</v>
       </c>
       <c r="H1444" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" s="1" t="n">
+        <v>46297.5625</v>
+      </c>
+      <c r="B1445" t="n">
+        <v>19000312</v>
+      </c>
+      <c r="C1445" t="n">
+        <v>45.3352012634277</v>
+      </c>
+      <c r="D1445" t="n">
+        <v>43.1500015258789</v>
+      </c>
+      <c r="E1445" t="n">
+        <v>45.1596984863281</v>
+      </c>
+      <c r="F1445" t="n">
+        <v>43.7700004577637</v>
+      </c>
+      <c r="G1445" t="n">
+        <v>43.7700004577637</v>
+      </c>
+      <c r="H1445" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37924,16 +37924,16 @@
         <v>46297.5625</v>
       </c>
       <c r="B1445" t="n">
-        <v>19000312</v>
+        <v>19036700</v>
       </c>
       <c r="C1445" t="n">
-        <v>45.3352012634277</v>
+        <v>45.3349990844727</v>
       </c>
       <c r="D1445" t="n">
         <v>43.1500015258789</v>
       </c>
       <c r="E1445" t="n">
-        <v>45.1596984863281</v>
+        <v>45.1599998474121</v>
       </c>
       <c r="F1445" t="n">
         <v>43.7700004577637</v>
@@ -37942,6 +37942,32 @@
         <v>43.7700004577637</v>
       </c>
       <c r="H1445" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" s="1" t="n">
+        <v>46300.5625</v>
+      </c>
+      <c r="B1446" t="n">
+        <v>16377481</v>
+      </c>
+      <c r="C1446" t="n">
+        <v>44.2200012207031</v>
+      </c>
+      <c r="D1446" t="n">
+        <v>42.2400016784668</v>
+      </c>
+      <c r="E1446" t="n">
+        <v>43.7700004577637</v>
+      </c>
+      <c r="F1446" t="n">
+        <v>42.9700012207031</v>
+      </c>
+      <c r="G1446" t="n">
+        <v>42.9700012207031</v>
+      </c>
+      <c r="H1446" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37924,7 +37924,7 @@
         <v>46297.5625</v>
       </c>
       <c r="B1445" t="n">
-        <v>19036700</v>
+        <v>19093800</v>
       </c>
       <c r="C1445" t="n">
         <v>45.3349990844727</v>
@@ -37950,7 +37950,7 @@
         <v>46300.5625</v>
       </c>
       <c r="B1446" t="n">
-        <v>16377481</v>
+        <v>16464500</v>
       </c>
       <c r="C1446" t="n">
         <v>44.2200012207031</v>
@@ -37968,6 +37968,32 @@
         <v>42.9700012207031</v>
       </c>
       <c r="H1446" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" s="1" t="n">
+        <v>46301.5625</v>
+      </c>
+      <c r="B1447" t="n">
+        <v>16205748</v>
+      </c>
+      <c r="C1447" t="n">
+        <v>45.3919982910156</v>
+      </c>
+      <c r="D1447" t="n">
+        <v>43</v>
+      </c>
+      <c r="E1447" t="n">
+        <v>43.560001373291</v>
+      </c>
+      <c r="F1447" t="n">
+        <v>43.2900009155273</v>
+      </c>
+      <c r="G1447" t="n">
+        <v>43.2900009155273</v>
+      </c>
+      <c r="H1447" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -37976,10 +37976,10 @@
         <v>46301.5625</v>
       </c>
       <c r="B1447" t="n">
-        <v>16205748</v>
+        <v>16358000</v>
       </c>
       <c r="C1447" t="n">
-        <v>45.3919982910156</v>
+        <v>45.4000015258789</v>
       </c>
       <c r="D1447" t="n">
         <v>43</v>
@@ -37994,6 +37994,32 @@
         <v>43.2900009155273</v>
       </c>
       <c r="H1447" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" s="1" t="n">
+        <v>46302.5625</v>
+      </c>
+      <c r="B1448" t="n">
+        <v>18768450</v>
+      </c>
+      <c r="C1448" t="n">
+        <v>42.3300018310547</v>
+      </c>
+      <c r="D1448" t="n">
+        <v>40.7601013183594</v>
+      </c>
+      <c r="E1448" t="n">
+        <v>42.189998626709</v>
+      </c>
+      <c r="F1448" t="n">
+        <v>41.3400001525879</v>
+      </c>
+      <c r="G1448" t="n">
+        <v>41.3400001525879</v>
+      </c>
+      <c r="H1448" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38002,13 +38002,13 @@
         <v>46302.5625</v>
       </c>
       <c r="B1448" t="n">
-        <v>18768450</v>
+        <v>19141000</v>
       </c>
       <c r="C1448" t="n">
-        <v>42.3300018310547</v>
+        <v>42.3800010681152</v>
       </c>
       <c r="D1448" t="n">
-        <v>40.7601013183594</v>
+        <v>40.7599983215332</v>
       </c>
       <c r="E1448" t="n">
         <v>42.189998626709</v>
@@ -38020,6 +38020,32 @@
         <v>41.3400001525879</v>
       </c>
       <c r="H1448" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" s="1" t="n">
+        <v>46303.5625</v>
+      </c>
+      <c r="B1449" t="n">
+        <v>22848240</v>
+      </c>
+      <c r="C1449" t="n">
+        <v>42.0099983215332</v>
+      </c>
+      <c r="D1449" t="n">
+        <v>38.8301010131836</v>
+      </c>
+      <c r="E1449" t="n">
+        <v>41.7099990844727</v>
+      </c>
+      <c r="F1449" t="n">
+        <v>39.4500007629395</v>
+      </c>
+      <c r="G1449" t="n">
+        <v>39.4500007629395</v>
+      </c>
+      <c r="H1449" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38028,13 +38028,13 @@
         <v>46303.5625</v>
       </c>
       <c r="B1449" t="n">
-        <v>22848240</v>
+        <v>23013700</v>
       </c>
       <c r="C1449" t="n">
         <v>42.0099983215332</v>
       </c>
       <c r="D1449" t="n">
-        <v>38.8301010131836</v>
+        <v>38.8300018310547</v>
       </c>
       <c r="E1449" t="n">
         <v>41.7099990844727</v>
@@ -38046,6 +38046,32 @@
         <v>39.4500007629395</v>
       </c>
       <c r="H1449" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" s="1" t="n">
+        <v>46304.5625</v>
+      </c>
+      <c r="B1450" t="n">
+        <v>13151483</v>
+      </c>
+      <c r="C1450" t="n">
+        <v>40.2400016784668</v>
+      </c>
+      <c r="D1450" t="n">
+        <v>38.9900016784668</v>
+      </c>
+      <c r="E1450" t="n">
+        <v>40</v>
+      </c>
+      <c r="F1450" t="n">
+        <v>39.8899993896484</v>
+      </c>
+      <c r="G1450" t="n">
+        <v>39.8899993896484</v>
+      </c>
+      <c r="H1450" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38054,7 +38054,7 @@
         <v>46304.5625</v>
       </c>
       <c r="B1450" t="n">
-        <v>13151483</v>
+        <v>13172900</v>
       </c>
       <c r="C1450" t="n">
         <v>40.2400016784668</v>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38106,7 +38106,7 @@
         <v>46308.5625</v>
       </c>
       <c r="B1452" t="n">
-        <v>23091252</v>
+        <v>23468100</v>
       </c>
       <c r="C1452" t="n">
         <v>35.9900016784668</v>
@@ -38124,6 +38124,32 @@
         <v>34.7299995422363</v>
       </c>
       <c r="H1452" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" s="1" t="n">
+        <v>46309.5625</v>
+      </c>
+      <c r="B1453" t="n">
+        <v>40667475</v>
+      </c>
+      <c r="C1453" t="n">
+        <v>33.3800010681152</v>
+      </c>
+      <c r="D1453" t="n">
+        <v>31.0450000762939</v>
+      </c>
+      <c r="E1453" t="n">
+        <v>33.1500015258789</v>
+      </c>
+      <c r="F1453" t="n">
+        <v>31.4200000762939</v>
+      </c>
+      <c r="G1453" t="n">
+        <v>31.4200000762939</v>
+      </c>
+      <c r="H1453" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38132,10 +38132,10 @@
         <v>46309.5625</v>
       </c>
       <c r="B1453" t="n">
-        <v>40667475</v>
+        <v>41353700</v>
       </c>
       <c r="C1453" t="n">
-        <v>33.3800010681152</v>
+        <v>33.3899993896484</v>
       </c>
       <c r="D1453" t="n">
         <v>31.0450000762939</v>
@@ -38150,6 +38150,32 @@
         <v>31.4200000762939</v>
       </c>
       <c r="H1453" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" s="1" t="n">
+        <v>46310.5625</v>
+      </c>
+      <c r="B1454" t="n">
+        <v>47713286</v>
+      </c>
+      <c r="C1454" t="n">
+        <v>34.3600006103516</v>
+      </c>
+      <c r="D1454" t="n">
+        <v>30.0300006866455</v>
+      </c>
+      <c r="E1454" t="n">
+        <v>30.5450000762939</v>
+      </c>
+      <c r="F1454" t="n">
+        <v>34.3499984741211</v>
+      </c>
+      <c r="G1454" t="n">
+        <v>34.3499984741211</v>
+      </c>
+      <c r="H1454" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -38158,7 +38158,7 @@
         <v>46310.5625</v>
       </c>
       <c r="B1454" t="n">
-        <v>47713286</v>
+        <v>48163300</v>
       </c>
       <c r="C1454" t="n">
         <v>34.3600006103516</v>
@@ -38176,6 +38176,32 @@
         <v>34.3499984741211</v>
       </c>
       <c r="H1454" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" s="1" t="n">
+        <v>46311.5625</v>
+      </c>
+      <c r="B1455" t="n">
+        <v>27713604</v>
+      </c>
+      <c r="C1455" t="n">
+        <v>33.6441993713379</v>
+      </c>
+      <c r="D1455" t="n">
+        <v>31.1049995422363</v>
+      </c>
+      <c r="E1455" t="n">
+        <v>33.0320014953613</v>
+      </c>
+      <c r="F1455" t="n">
+        <v>31.2800006866455</v>
+      </c>
+      <c r="G1455" t="n">
+        <v>31.2800006866455</v>
+      </c>
+      <c r="H1455" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42567,7 +42567,7 @@
         <v>31.2800006866455</v>
       </c>
       <c r="H1455" t="n">
-        <v>28066800</v>
+        <v>28282300</v>
       </c>
       <c r="I1455" t="s">
         <v>9</v>
@@ -42584,7 +42584,7 @@
         <v>32.3499984741211</v>
       </c>
       <c r="D1456" t="n">
-        <v>32.4300003051758</v>
+        <v>32.439998626709</v>
       </c>
       <c r="E1456" t="n">
         <v>30.2900009155273</v>
@@ -42596,9 +42596,38 @@
         <v>30.7800006866455</v>
       </c>
       <c r="H1456" t="n">
-        <v>24740645</v>
+        <v>25941800</v>
       </c>
       <c r="I1456" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1457" s="1" t="n">
+        <v>46315.5625</v>
+      </c>
+      <c r="C1457" t="n">
+        <v>30.2800006866455</v>
+      </c>
+      <c r="D1457" t="n">
+        <v>32.1599998474121</v>
+      </c>
+      <c r="E1457" t="n">
+        <v>30.1949996948242</v>
+      </c>
+      <c r="F1457" t="n">
+        <v>31.2600002288818</v>
+      </c>
+      <c r="G1457" t="n">
+        <v>31.2600002288818</v>
+      </c>
+      <c r="H1457" t="n">
+        <v>20469150</v>
+      </c>
+      <c r="I1457" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42613,10 +42613,10 @@
         <v>30.2800006866455</v>
       </c>
       <c r="D1457" t="n">
-        <v>32.1599998474121</v>
+        <v>32.1699981689453</v>
       </c>
       <c r="E1457" t="n">
-        <v>30.1949996948242</v>
+        <v>30.1900005340576</v>
       </c>
       <c r="F1457" t="n">
         <v>31.2600002288818</v>
@@ -42625,9 +42625,38 @@
         <v>31.2600002288818</v>
       </c>
       <c r="H1457" t="n">
-        <v>20469150</v>
+        <v>20760100</v>
       </c>
       <c r="I1457" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1458" s="1" t="n">
+        <v>46316.5625</v>
+      </c>
+      <c r="C1458" t="n">
+        <v>31.5599994659424</v>
+      </c>
+      <c r="D1458" t="n">
+        <v>32.5200004577637</v>
+      </c>
+      <c r="E1458" t="n">
+        <v>31.2900009155273</v>
+      </c>
+      <c r="F1458" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="G1458" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="H1458" t="n">
+        <v>16657792</v>
+      </c>
+      <c r="I1458" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42654,9 +42654,38 @@
         <v>32.2799987792969</v>
       </c>
       <c r="H1458" t="n">
-        <v>16657792</v>
+        <v>16836800</v>
       </c>
       <c r="I1458" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1459" s="1" t="n">
+        <v>46317.5625</v>
+      </c>
+      <c r="C1459" t="n">
+        <v>30.9400005340576</v>
+      </c>
+      <c r="D1459" t="n">
+        <v>32.3400001525879</v>
+      </c>
+      <c r="E1459" t="n">
+        <v>30.7000007629395</v>
+      </c>
+      <c r="F1459" t="n">
+        <v>31.1599998474121</v>
+      </c>
+      <c r="G1459" t="n">
+        <v>31.1599998474121</v>
+      </c>
+      <c r="H1459" t="n">
+        <v>18829307</v>
+      </c>
+      <c r="I1459" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42683,9 +42683,38 @@
         <v>31.1599998474121</v>
       </c>
       <c r="H1459" t="n">
-        <v>18829307</v>
+        <v>18980000</v>
       </c>
       <c r="I1459" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1460" s="1" t="n">
+        <v>46318.5625</v>
+      </c>
+      <c r="C1460" t="n">
+        <v>30.9200000762939</v>
+      </c>
+      <c r="D1460" t="n">
+        <v>31.5699996948242</v>
+      </c>
+      <c r="E1460" t="n">
+        <v>30.3799991607666</v>
+      </c>
+      <c r="F1460" t="n">
+        <v>31.2700004577637</v>
+      </c>
+      <c r="G1460" t="n">
+        <v>31.2700004577637</v>
+      </c>
+      <c r="H1460" t="n">
+        <v>12969878</v>
+      </c>
+      <c r="I1460" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42700,7 +42700,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="D1460" t="n">
-        <v>31.5699996948242</v>
+        <v>31.5799999237061</v>
       </c>
       <c r="E1460" t="n">
         <v>30.3799991607666</v>
@@ -42712,9 +42712,38 @@
         <v>31.2700004577637</v>
       </c>
       <c r="H1460" t="n">
-        <v>12969878</v>
+        <v>12999800</v>
       </c>
       <c r="I1460" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1461" s="1" t="n">
+        <v>46321.5625</v>
+      </c>
+      <c r="C1461" t="n">
+        <v>30.9400005340576</v>
+      </c>
+      <c r="D1461" t="n">
+        <v>31.5172004699707</v>
+      </c>
+      <c r="E1461" t="n">
+        <v>29.9400005340576</v>
+      </c>
+      <c r="F1461" t="n">
+        <v>30.7600002288818</v>
+      </c>
+      <c r="G1461" t="n">
+        <v>30.7600002288818</v>
+      </c>
+      <c r="H1461" t="n">
+        <v>17017605</v>
+      </c>
+      <c r="I1461" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42712,7 +42712,7 @@
         <v>31.2700004577637</v>
       </c>
       <c r="H1460" t="n">
-        <v>12999800</v>
+        <v>13094000</v>
       </c>
       <c r="I1460" t="s">
         <v>9</v>
@@ -42729,7 +42729,7 @@
         <v>30.9400005340576</v>
       </c>
       <c r="D1461" t="n">
-        <v>31.5172004699707</v>
+        <v>31.5200004577637</v>
       </c>
       <c r="E1461" t="n">
         <v>29.9400005340576</v>
@@ -42741,9 +42741,38 @@
         <v>30.7600002288818</v>
       </c>
       <c r="H1461" t="n">
-        <v>17017605</v>
+        <v>17114200</v>
       </c>
       <c r="I1461" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1462" s="1" t="n">
+        <v>46322.5625</v>
+      </c>
+      <c r="C1462" t="n">
+        <v>31.1900005340576</v>
+      </c>
+      <c r="D1462" t="n">
+        <v>33.3050003051758</v>
+      </c>
+      <c r="E1462" t="n">
+        <v>31.0699996948242</v>
+      </c>
+      <c r="F1462" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="G1462" t="n">
+        <v>32.9500007629395</v>
+      </c>
+      <c r="H1462" t="n">
+        <v>21943263</v>
+      </c>
+      <c r="I1462" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42770,9 +42770,38 @@
         <v>32.9500007629395</v>
       </c>
       <c r="H1462" t="n">
-        <v>21943263</v>
+        <v>22094500</v>
       </c>
       <c r="I1462" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1463" s="1" t="n">
+        <v>46323.5625</v>
+      </c>
+      <c r="C1463" t="n">
+        <v>33.0750007629395</v>
+      </c>
+      <c r="D1463" t="n">
+        <v>33.310001373291</v>
+      </c>
+      <c r="E1463" t="n">
+        <v>31.6499996185303</v>
+      </c>
+      <c r="F1463" t="n">
+        <v>32.4300003051758</v>
+      </c>
+      <c r="G1463" t="n">
+        <v>32.4300003051758</v>
+      </c>
+      <c r="H1463" t="n">
+        <v>14988950</v>
+      </c>
+      <c r="I1463" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42799,9 +42799,38 @@
         <v>32.4300003051758</v>
       </c>
       <c r="H1463" t="n">
-        <v>14988950</v>
+        <v>15218900</v>
       </c>
       <c r="I1463" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1464" s="1" t="n">
+        <v>46324.5625</v>
+      </c>
+      <c r="C1464" t="n">
+        <v>31.7399997711182</v>
+      </c>
+      <c r="D1464" t="n">
+        <v>32.5299987792969</v>
+      </c>
+      <c r="E1464" t="n">
+        <v>30.9699993133545</v>
+      </c>
+      <c r="F1464" t="n">
+        <v>31.7199993133545</v>
+      </c>
+      <c r="G1464" t="n">
+        <v>31.7199993133545</v>
+      </c>
+      <c r="H1464" t="n">
+        <v>13034313</v>
+      </c>
+      <c r="I1464" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IONQ.xlsx
+++ b/data/IONQ.xlsx
@@ -42816,7 +42816,7 @@
         <v>31.7399997711182</v>
       </c>
       <c r="D1464" t="n">
-        <v>32.5299987792969</v>
+        <v>32.5400009155273</v>
       </c>
       <c r="E1464" t="n">
         <v>30.9699993133545</v>
@@ -42828,9 +42828,38 @@
         <v>31.7199993133545</v>
       </c>
       <c r="H1464" t="n">
-        <v>13034313</v>
+        <v>13360300</v>
       </c>
       <c r="I1464" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1465" s="1" t="n">
+        <v>46325.5625</v>
+      </c>
+      <c r="C1465" t="n">
+        <v>29.8299999237061</v>
+      </c>
+      <c r="D1465" t="n">
+        <v>30.3700008392334</v>
+      </c>
+      <c r="E1465" t="n">
+        <v>28.5450000762939</v>
+      </c>
+      <c r="F1465" t="n">
+        <v>30.0400009155273</v>
+      </c>
+      <c r="G1465" t="n">
+        <v>30.0400009155273</v>
+      </c>
+      <c r="H1465" t="n">
+        <v>23331370</v>
+      </c>
+      <c r="I1465" t="s">
         <v>9</v>
       </c>
     </row>
